--- a/_ForDRA/BVSimulationFiles/96.xlsx
+++ b/_ForDRA/BVSimulationFiles/96.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000198581560283688</v>
+        <v>0.00397163120567376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002035291494446851</v>
+        <v>0.004070582988893702</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002079284904985453</v>
+        <v>0.004158569809970906</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002118105617442589</v>
+        <v>0.004236211234885178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002152048878897823</v>
+        <v>0.004304097757795645</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002181396024559869</v>
+        <v>0.004362792049119739</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002206415076381626</v>
+        <v>0.004412830152763252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002227361317251402</v>
+        <v>0.004454722634502804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002244477841722618</v>
+        <v>0.004488955683445236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000225799608420723</v>
+        <v>0.00451599216841446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002268136325522574</v>
+        <v>0.004536272651045148</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002275108178647058</v>
+        <v>0.004550216357294116</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002279111054507199</v>
+        <v>0.004558222109014398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002280334608586762</v>
+        <v>0.004560669217173524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000227895916911831</v>
+        <v>0.00455791833823662</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002275156147588046</v>
+        <v>0.004550312295176092</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002269088432256658</v>
+        <v>0.004538176864513317</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002260910765371653</v>
+        <v>0.004521821530743306</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000225077010472057</v>
+        <v>0.00450154020944114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002238805970149253</v>
+        <v>0.004477611940298506</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000198581560283688</v>
+        <v>0.00397163120567376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002035291494446851</v>
+        <v>0.004070582988893702</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002079284904985453</v>
+        <v>0.004158569809970906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002118105617442589</v>
+        <v>0.004236211234885178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002152048878897823</v>
+        <v>0.004304097757795645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002181396024559869</v>
+        <v>0.004362792049119739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002206415076381626</v>
+        <v>0.004412830152763252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002227361317251402</v>
+        <v>0.004454722634502804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002244477841722618</v>
+        <v>0.004488955683445236</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000225799608420723</v>
+        <v>0.00451599216841446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002268136325522574</v>
+        <v>0.004536272651045148</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002275108178647058</v>
+        <v>0.004550216357294116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0002279111054507199</v>
+        <v>0.004558222109014398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002280334608586762</v>
+        <v>0.004560669217173524</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000227895916911831</v>
+        <v>0.00455791833823662</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002275156147588046</v>
+        <v>0.004550312295176092</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002269088432256658</v>
+        <v>0.004538176864513317</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002260910765371653</v>
+        <v>0.004521821530743306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000225077010472057</v>
+        <v>0.00450154020944114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002238805970149253</v>
+        <v>0.004477611940298506</v>
       </c>
     </row>
   </sheetData>
